--- a/AAII_Financials/Yearly/IMCI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IMCI_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
